--- a/results/Int Task Remove ACC -0.0/Rando_1_permute.xlsx
+++ b/results/Int Task Remove ACC -0.0/Rando_1_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6983863074487417</v>
+        <v>0.7043088505962269</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7010191716774681</v>
+        <v>0.7075351633482293</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7019667395865017</v>
+        <v>0.7118511304524149</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6801704842344978</v>
+        <v>0.7162370440560586</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6801704842344978</v>
+        <v>0.7153998795067967</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6790381795777669</v>
+        <v>0.7182403897896633</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6759091095201328</v>
+        <v>0.7138205996584076</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6813802905874922</v>
+        <v>0.7071515543233273</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6943194181231136</v>
+        <v>0.691202533866779</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6879367391185669</v>
+        <v>0.6753059123558176</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6994791301092628</v>
+        <v>0.6767791757329028</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6126528586914983</v>
+        <v>0.6627121304290182</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6097063319373279</v>
+        <v>0.6147502788111338</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6242968792650305</v>
+        <v>0.6160770688566014</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6258400891415736</v>
+        <v>0.6216160029791847</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6217590642864385</v>
+        <v>0.6327682046122771</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6001387719051964</v>
+        <v>0.5803570732239925</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5806704920334105</v>
+        <v>0.5806073695826802</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5828454138493093</v>
+        <v>0.5775636001341413</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5937582863448836</v>
+        <v>0.579914484920802</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.567070162919289</v>
+        <v>0.5856042792634707</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5635891669201314</v>
+        <v>0.5840544890542259</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5563037637553325</v>
+        <v>0.5840544890542259</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5542326649665037</v>
+        <v>0.5626004110027063</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5316638298121241</v>
+        <v>0.5608878184881028</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5363273359693659</v>
+        <v>0.564326164182713</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5294277352737028</v>
+        <v>0.5643534603776234</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5132557146533774</v>
+        <v>0.5585620364521185</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5250374347815914</v>
+        <v>0.5547018183165267</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5183388998073668</v>
+        <v>0.5585664233405864</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5120086197484071</v>
+        <v>0.5396228640727483</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5097976279606623</v>
+        <v>0.5292083908503155</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5217280148647279</v>
+        <v>0.5482504113926518</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5032367925411197</v>
+        <v>0.5496176582984332</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5033766855400357</v>
+        <v>0.5494438887719052</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5072390971198615</v>
+        <v>0.5483564278639558</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5072390971198615</v>
+        <v>0.5311712797236066</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5080358048088096</v>
+        <v>0.5306095142837088</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.4879774884381117</v>
+        <v>0.5313811192219804</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5009253897506687</v>
+        <v>0.5310652632523026</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4982947189661761</v>
+        <v>0.5317308517192704</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5228330233265482</v>
+        <v>0.5314149957495925</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5202318421812</v>
+        <v>0.51626706987046</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5043647103093829</v>
+        <v>0.5023148148148148</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5048531172254588</v>
+        <v>0.5027705637834086</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5017196602793571</v>
+        <v>0.5023847613142728</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4947030758912208</v>
+        <v>0.5065586419753086</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4934396520125094</v>
+        <v>0.5011574074074074</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4929817095996818</v>
+        <v>0.5042438271604939</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.4846449154987795</v>
+        <v>0.5015432098765432</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.4786031952145871</v>
+        <v>0.5015432098765432</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5029184994111822</v>
+        <v>0.5007716049382716</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5081415775640875</v>
+        <v>0.5003858024691358</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4996561166873338</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4996561166873338</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4713253472465939</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.4744358948862529</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4703341541689089</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.458514170624615</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.474556046887064</v>
+        <v>0.5003858024691358</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4756118247116352</v>
+        <v>0.5003858024691358</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4754019852132613</v>
+        <v>0.5003858024691358</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4672640633895635</v>
+        <v>0.5005256954680518</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4662060921207584</v>
+        <v>0.5001398929989159</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4588539107648394</v>
+        <v>0.5001398929989159</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4534297668904955</v>
+        <v>0.5002797859978318</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4920368225669342</v>
+        <v>0.500069946499458</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4753915054241439</v>
+        <v>0.5004896254962058</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4634764726297154</v>
+        <v>0.5004896254962058</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4651617689494085</v>
+        <v>0.5004896254962058</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.475163143507795</v>
+        <v>0.5004896254962058</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4723182463364607</v>
+        <v>0.5008054814658837</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4707750364599175</v>
+        <v>0.5027344938115627</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.469583752524898</v>
+        <v>0.5023486913424269</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4843141928515165</v>
+        <v>0.5025585308408008</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4740057361003876</v>
+        <v>0.5019967654009031</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4740057361003876</v>
+        <v>0.4996480740584763</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4765730407181239</v>
+        <v>0.4996480740584763</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4765730407181239</v>
+        <v>0.5000338765276121</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4698186947739486</v>
+        <v>0.5013672469057813</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4687268469775313</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4615976657853895</v>
+        <v>0.4996841440303222</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4759849539474197</v>
+        <v>0.4993682880606444</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4883579291546759</v>
+        <v>0.4996841440303222</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4883579291546759</v>
+        <v>0.5003858024691358</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5320596246383255</v>
+        <v>0.500069946499458</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5297448098235106</v>
+        <v>0.500069946499458</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5249194762250142</v>
+        <v>0.5002437160259859</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4921428390382381</v>
+        <v>0.5009431810205658</v>
       </c>
     </row>
   </sheetData>
